--- a/report_templates/Installation Status.xlsx
+++ b/report_templates/Installation Status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git hub repositeries\GRP_SYS\report_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b68409331e52ac1/Documents/GRP/GRP_SYS/report_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871F2045-2E24-45DD-9E9D-69903C07EC71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{871F2045-2E24-45DD-9E9D-69903C07EC71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6748204F-CF6E-4E25-9082-67D41AD5B46B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t xml:space="preserve">           CUSTOMER</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">   PHONE NUMBER</t>
   </si>
@@ -47,44 +44,50 @@
     <t xml:space="preserve">   BRAND</t>
   </si>
   <si>
-    <t xml:space="preserve">                   REMARKS</t>
-  </si>
-  <si>
     <t>INST.START</t>
   </si>
   <si>
     <t xml:space="preserve">     TANK SIZE</t>
   </si>
   <si>
-    <t xml:space="preserve">                               WORKERS</t>
-  </si>
-  <si>
     <t xml:space="preserve"> TYPE</t>
   </si>
   <si>
-    <t xml:space="preserve">   CONT.PER.</t>
-  </si>
-  <si>
-    <t>SALES PER.</t>
-  </si>
-  <si>
     <t>LOCATION</t>
   </si>
   <si>
-    <t xml:space="preserve">  INS.STATUS </t>
-  </si>
-  <si>
     <t>INS.COMPL.DATE</t>
   </si>
   <si>
-    <t xml:space="preserve">WO </t>
+    <t xml:space="preserve"> WORKERS</t>
+  </si>
+  <si>
+    <t>W.O.NO.</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>INSTALLATION STATUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CONTACT PERSON</t>
+  </si>
+  <si>
+    <t>SALES PERSON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  REMARKS</t>
+  </si>
+  <si>
+    <t>Qty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +98,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -123,9 +134,15 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -135,16 +152,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -160,6 +190,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,103 +462,107 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.453125" customWidth="1"/>
     <col min="2" max="2" width="33.453125" customWidth="1"/>
-    <col min="3" max="3" width="29.453125" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" customWidth="1"/>
-    <col min="5" max="5" width="5.81640625" customWidth="1"/>
-    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.81640625" customWidth="1"/>
-    <col min="9" max="9" width="63.26953125" customWidth="1"/>
-    <col min="10" max="10" width="16.453125" customWidth="1"/>
-    <col min="11" max="11" width="20.26953125" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="25.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="6" max="6" width="7.90625" customWidth="1"/>
+    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.54296875" customWidth="1"/>
+    <col min="10" max="10" width="37.1796875" customWidth="1"/>
+    <col min="11" max="11" width="18.26953125" customWidth="1"/>
+    <col min="12" max="12" width="20.26953125" customWidth="1"/>
+    <col min="13" max="13" width="17.81640625" customWidth="1"/>
+    <col min="14" max="14" width="13.90625" customWidth="1"/>
+    <col min="15" max="15" width="35.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="G5" s="3"/>
-      <c r="K5" s="2"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="G6" s="6"/>
-      <c r="P6" s="7"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="G10" s="3"/>
-      <c r="K10" s="2"/>
-      <c r="N10" s="4"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5"/>
+      <c r="H5" s="6"/>
+      <c r="L5" s="5"/>
+      <c r="N5" s="7"/>
+    </row>
+    <row r="6" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="H6" s="6"/>
+      <c r="Q6" s="7"/>
+    </row>
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="1"/>
+      <c r="H10" s="2"/>
+      <c r="L10" s="1"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/report_templates/Installation Status.xlsx
+++ b/report_templates/Installation Status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b68409331e52ac1/Documents/GRP/GRP_SYS/report_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{871F2045-2E24-45DD-9E9D-69903C07EC71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6748204F-CF6E-4E25-9082-67D41AD5B46B}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{871F2045-2E24-45DD-9E9D-69903C07EC71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{264479D7-2CC9-43E1-88F9-3AC28640A567}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,18 +47,12 @@
     <t>INST.START</t>
   </si>
   <si>
-    <t xml:space="preserve">     TANK SIZE</t>
-  </si>
-  <si>
     <t xml:space="preserve"> TYPE</t>
   </si>
   <si>
     <t>LOCATION</t>
   </si>
   <si>
-    <t>INS.COMPL.DATE</t>
-  </si>
-  <si>
     <t xml:space="preserve"> WORKERS</t>
   </si>
   <si>
@@ -81,6 +75,12 @@
   </si>
   <si>
     <t>Qty</t>
+  </si>
+  <si>
+    <t>TANK SIZE/MATERIAL</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -462,106 +462,105 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.453125" customWidth="1"/>
     <col min="2" max="2" width="33.453125" customWidth="1"/>
-    <col min="3" max="3" width="25.54296875" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="6" max="6" width="7.90625" customWidth="1"/>
-    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.1796875" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" customWidth="1"/>
+    <col min="7" max="7" width="7.90625" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29.54296875" customWidth="1"/>
     <col min="10" max="10" width="37.1796875" customWidth="1"/>
     <col min="11" max="11" width="18.26953125" customWidth="1"/>
     <col min="12" max="12" width="20.26953125" customWidth="1"/>
-    <col min="13" max="13" width="17.81640625" customWidth="1"/>
-    <col min="14" max="14" width="13.90625" customWidth="1"/>
-    <col min="15" max="15" width="35.6328125" customWidth="1"/>
+    <col min="13" max="13" width="13.90625" customWidth="1"/>
+    <col min="14" max="14" width="35.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>5</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="H5" s="6"/>
       <c r="L5" s="5"/>
-      <c r="N5" s="7"/>
-    </row>
-    <row r="6" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="M5" s="7"/>
+    </row>
+    <row r="6" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="H6" s="6"/>
-      <c r="Q6" s="7"/>
-    </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="P6" s="7"/>
+    </row>
+    <row r="7" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P7" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="H10" s="2"/>
       <c r="L10" s="1"/>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
     </row>
   </sheetData>
